--- a/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T06:38:46+00:00</t>
+    <t>2026-03-30T12:35:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:35:15+00:00</t>
+    <t>2026-04-02T07:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:51:30+00:00</t>
+    <t>2026-04-02T10:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T10:28:37+00:00</t>
+    <t>2026-04-02T10:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T10:54:32+00:00</t>
+    <t>2026-04-02T12:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:29:02+00:00</t>
+    <t>2026-04-10T08:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T08:03:47+00:00</t>
+    <t>2026-04-13T14:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:24:26+00:00</t>
+    <t>2026-04-14T04:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
